--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationtiming.xlsx
@@ -264,7 +264,7 @@
 A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -329,7 +329,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -392,7 +392,7 @@
     <t>スケジュールされたタイミングの多くは規則的な繰り返しで決定されている。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
